--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -90,6 +90,18 @@
   </si>
   <si>
     <t>7654321</t>
+  </si>
+  <si>
+    <t>SATRA</t>
+  </si>
+  <si>
+    <t>666</t>
+  </si>
+  <si>
+    <t>MN_MT_TESTSTF</t>
+  </si>
+  <si>
+    <t>123 Nguyễn Huệ, Phường Bến Nghé, Quận 1, Tp.HCM, VNM</t>
   </si>
 </sst>
 </file>
@@ -446,6 +458,20 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -102,6 +102,18 @@
   </si>
   <si>
     <t>123 Nguyễn Huệ, Phường Bến Nghé, Quận 1, Tp.HCM, VNM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>BLANK_A_TESTCODE</t>
+  </si>
+  <si>
+    <t>456 Le Loi, Phuong Ben Thanh, Quan 1, Tp.HCM, VNM</t>
   </si>
 </sst>
 </file>
@@ -472,6 +484,20 @@
         <v>28</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -114,6 +114,18 @@
   </si>
   <si>
     <t>456 Le Loi, Phuong Ben Thanh, Quan 1, Tp.HCM, VNM</t>
+  </si>
+  <si>
+    <t>8934563112223</t>
+  </si>
+  <si>
+    <t>BigC Test Product A</t>
+  </si>
+  <si>
+    <t>8934563112230</t>
+  </si>
+  <si>
+    <t>BigC Test Product B</t>
   </si>
 </sst>
 </file>
@@ -557,6 +569,34 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>2.5</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5">
+        <v>1.5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -126,6 +126,18 @@
   </si>
   <si>
     <t>BigC Test Product B</t>
+  </si>
+  <si>
+    <t>WINMART</t>
+  </si>
+  <si>
+    <t>WM001</t>
+  </si>
+  <si>
+    <t>MN_MT_TESTWIN</t>
+  </si>
+  <si>
+    <t>789 Trần Hưng Đạo, Phường Cầu Kho, Quận 1, Tp.HCM, VNM</t>
   </si>
 </sst>
 </file>
@@ -510,6 +522,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -1,149 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MaKH" sheetId="1" r:id="rId1"/>
-    <sheet name="SanPham" sheetId="2" r:id="rId5"/>
+    <sheet name="MaKH" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SanPham" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t>Hệ thống</t>
-  </si>
-  <si>
-    <t>Mã ST</t>
-  </si>
-  <si>
-    <t>Mã KH</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>KH-COOP-001</t>
-  </si>
-  <si>
-    <t>COOPFOOD</t>
-  </si>
-  <si>
-    <t>888</t>
-  </si>
-  <si>
-    <t>KH-CF-002</t>
-  </si>
-  <si>
-    <t>12 Nguyễn Huệ</t>
-  </si>
-  <si>
-    <t>LOTTE</t>
-  </si>
-  <si>
-    <t>777</t>
-  </si>
-  <si>
-    <t>KH-LOTTE-003</t>
-  </si>
-  <si>
-    <t>Mã hàng Công ty</t>
-  </si>
-  <si>
-    <t>Tên hàng</t>
-  </si>
-  <si>
-    <t>Trọng lượng kg</t>
-  </si>
-  <si>
-    <t>Quy cách thùng</t>
-  </si>
-  <si>
-    <t>Mã hàng Coop</t>
-  </si>
-  <si>
-    <t>SP0001</t>
-  </si>
-  <si>
-    <t>Nước giặt Blue</t>
-  </si>
-  <si>
-    <t>1234567</t>
-  </si>
-  <si>
-    <t>SP0002</t>
-  </si>
-  <si>
-    <t>Chai tay toilet</t>
-  </si>
-  <si>
-    <t>7654321</t>
-  </si>
-  <si>
-    <t>SATRA</t>
-  </si>
-  <si>
-    <t>666</t>
-  </si>
-  <si>
-    <t>MN_MT_TESTSTF</t>
-  </si>
-  <si>
-    <t>123 Nguyễn Huệ, Phường Bến Nghé, Quận 1, Tp.HCM, VNM</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>555</t>
-  </si>
-  <si>
-    <t>BLANK_A_TESTCODE</t>
-  </si>
-  <si>
-    <t>456 Le Loi, Phuong Ben Thanh, Quan 1, Tp.HCM, VNM</t>
-  </si>
-  <si>
-    <t>8934563112223</t>
-  </si>
-  <si>
-    <t>BigC Test Product A</t>
-  </si>
-  <si>
-    <t>8934563112230</t>
-  </si>
-  <si>
-    <t>BigC Test Product B</t>
-  </si>
-  <si>
-    <t>WINMART</t>
-  </si>
-  <si>
-    <t>WM001</t>
-  </si>
-  <si>
-    <t>MN_MT_TESTWIN</t>
-  </si>
-  <si>
-    <t>789 Trần Hưng Đạo, Phường Cầu Kho, Quận 1, Tp.HCM, VNM</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -154,7 +27,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -173,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,189 +380,328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mã ST</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Mã KH</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Địa chỉ</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COOP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KH-COOP-001</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COOPFOOD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KH-CF-002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12 Nguyễn Huệ</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LOTTE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KH-LOTTE-003</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SATRA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MN_MT_TESTSTF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>123 Nguyễn Huệ, Phường Bến Nghé, Quận 1, Tp.HCM, VNM</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BLANK_A_TESTCODE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>456 Le Loi, Phuong Ben Thanh, Quan 1, Tp.HCM, VNM</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WINMART</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WM001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MN_MT_TESTWIN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>789 Trần Hưng Đạo, Phường Cầu Kho, Quận 1, Tp.HCM, VNM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Maxidi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_GC_00002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LA_GC_00002</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mã hàng Công ty</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tên hàng</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Trọng lượng kg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Quy cách thùng</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Mã hàng Coop</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Mã hàng BigC</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SP0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nước giặt Blue</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>3.6</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>21</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SP0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chai tay toilet</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>0.18</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>48</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7654321</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>8934563112223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BigC Test Product A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>2.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8934563112230</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BigC Test Product B</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GC02344</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nước tẩy Javel Cleanwise 550G</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>280085</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8935355302344</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GO/internal/processing/productdata/testdata/data.xlsx
+++ b/GO/internal/processing/productdata/testdata/data.xlsx
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>555</t>
@@ -542,6 +541,278 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>LA_GC_00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GO! DONG NAI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BIGCDONGNAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GO! AN LAC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BIGCANLAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GO! DA NANG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIGCDANANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GO! GO VAP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BIGCGOVAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GO! PHU THANH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BIGCPHUTHANH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GO! TAN HIEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BIGCTANHIEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GO! TRUONG CHINH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BIGCTRUONGCHINH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GO! DI AN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BIGCDIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GO! DA LAT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BIGCDALAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GO! QUY NHON</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BIGCQUYNHON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GO! NGUYEN THI THAP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BIGNGUYENTHITHAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GO! MY THO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BIGCMYTHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GO! QUANG NGAI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BIGCQUANGNGAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GO! BUON MA THUOT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BIGCBUONMATHUOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GO! BA RIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BIGCBARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BIGC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GO! NINH THUAN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BIGCNINH THUAN</t>
         </is>
       </c>
     </row>
